--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -13101,16 +13101,16 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O74" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>5.959010722394861</v>
+        <v>6.012374997520785</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -13263,10 +13263,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O75" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -14781,16 +14781,16 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="O84" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.7648879434715791</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -14943,10 +14943,10 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="O85" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5645</v>
+        <v>5687</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -15654,6 +15654,154 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15687,7 +15835,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -15770,7 +15918,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -15780,7 +15928,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>38</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>86</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.954728336492448</v>
       </c>
@@ -1306,9 +1300,6 @@
       <c r="O5" t="n">
         <v>122</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>2.170147188454248</v>
       </c>
@@ -1702,9 +1693,6 @@
       <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -1850,9 +1838,6 @@
       <c r="O8" t="n">
         <v>34</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.6014517807704721</v>
       </c>
@@ -2838,9 +2823,6 @@
       <c r="O14" t="n">
         <v>36</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3231,9 +3213,6 @@
       <c r="O16" t="n">
         <v>131</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>1.454295489308264</v>
       </c>
@@ -3379,9 +3358,6 @@
       <c r="O17" t="n">
         <v>125</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>2.223511463580172</v>
       </c>
@@ -3775,9 +3751,6 @@
       <c r="O19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -3923,9 +3896,6 @@
       <c r="O20" t="n">
         <v>26</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.4599337147068316</v>
       </c>
@@ -4911,9 +4881,6 @@
       <c r="O26" t="n">
         <v>36</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5304,9 +5271,6 @@
       <c r="O28" t="n">
         <v>261</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>2.897489486331732</v>
       </c>
@@ -5452,9 +5416,6 @@
       <c r="O29" t="n">
         <v>116</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>2.063418638202399</v>
       </c>
@@ -5848,9 +5809,6 @@
       <c r="O31" t="n">
         <v>4</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.007751879695168184</v>
       </c>
@@ -5996,9 +5954,6 @@
       <c r="O32" t="n">
         <v>27</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.4776234729647867</v>
       </c>
@@ -7132,9 +7087,6 @@
       <c r="O39" t="n">
         <v>58</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="S39" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7525,9 +7477,6 @@
       <c r="O41" t="n">
         <v>392</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>4.351784975639996</v>
       </c>
@@ -7673,9 +7622,6 @@
       <c r="O42" t="n">
         <v>113</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>2.010054363076475</v>
       </c>
@@ -8069,9 +8015,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8217,9 +8160,6 @@
       <c r="O45" t="n">
         <v>21</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.3714849234170563</v>
       </c>
@@ -9205,9 +9145,6 @@
       <c r="O51" t="n">
         <v>146</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="S51" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9598,9 +9535,6 @@
       <c r="O53" t="n">
         <v>872</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>9.680501272342031</v>
       </c>
@@ -9746,9 +9680,6 @@
       <c r="O54" t="n">
         <v>106</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>1.885537721115986</v>
       </c>
@@ -10142,9 +10073,6 @@
       <c r="O56" t="n">
         <v>3</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -10290,9 +10218,6 @@
       <c r="O57" t="n">
         <v>45</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.7960391216079779</v>
       </c>
@@ -11426,9 +11351,6 @@
       <c r="O64" t="n">
         <v>2137</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>23.72388901260885</v>
       </c>
@@ -11574,9 +11496,6 @@
       <c r="O65" t="n">
         <v>197</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>3.504254066602351</v>
       </c>
@@ -11970,9 +11889,6 @@
       <c r="O67" t="n">
         <v>5</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.009689849618960231</v>
       </c>
@@ -12113,16 +12029,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O68" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="R68" t="n">
-        <v>0.9906264624454836</v>
+        <v>1.008316220703439</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -12275,10 +12188,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O69" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -12514,9 +12427,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -12662,9 +12572,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -12810,9 +12717,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12958,9 +12862,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13106,9 +13007,6 @@
       <c r="O74" t="n">
         <v>338</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>6.012374997520785</v>
       </c>
@@ -13497,16 +13395,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O76" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -13645,16 +13540,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O77" t="n">
-        <v>99</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="R77" t="n">
-        <v>1.751286067537551</v>
+        <v>1.786665584053461</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -13807,10 +13699,10 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O78" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -14046,9 +13938,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -14194,9 +14083,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -14342,9 +14228,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -14490,9 +14373,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -14638,9 +14518,6 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -14781,16 +14658,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O84" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R84" t="n">
-        <v>0.7648879434715791</v>
+        <v>0.8716164937234273</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -14943,10 +14817,10 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="O85" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -15177,16 +15051,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -15325,16 +15196,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="O87" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R87" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.6368312972863822</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15487,10 +15355,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="O88" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -15724,9 +15592,6 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
@@ -15980,7 +15845,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5687</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O28" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R28" t="n">
-        <v>2.897489486331732</v>
+        <v>2.908590978616528</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -7472,13 +7472,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O41" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="R41" t="n">
-        <v>4.351784975639996</v>
+        <v>4.362886467924791</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -9530,13 +9530,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="O53" t="n">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="R53" t="n">
-        <v>9.680501272342031</v>
+        <v>9.702704256911622</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -11346,13 +11346,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2137</v>
+        <v>2143</v>
       </c>
       <c r="O64" t="n">
-        <v>2137</v>
+        <v>2143</v>
       </c>
       <c r="R64" t="n">
-        <v>23.72388901260885</v>
+        <v>23.79049796631763</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -14658,13 +14658,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="O84" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="R84" t="n">
-        <v>0.8716164937234273</v>
+        <v>1.067285502518482</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="O85" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5729</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -15051,13 +15051,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R86" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5750</v>
+        <v>5752</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -14658,13 +14658,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="O84" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="R84" t="n">
-        <v>1.067285502518482</v>
+        <v>1.387471153274027</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -14817,10 +14817,10 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="O85" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5752</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -9140,10 +9140,10 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="O51" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="O52" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -11307,12 +11307,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -11346,81 +11346,92 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2143</v>
+        <v>421</v>
       </c>
       <c r="O64" t="n">
-        <v>2143</v>
-      </c>
-      <c r="R64" t="n">
-        <v>23.79049796631763</v>
+        <v>421</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11447,17 +11458,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -11491,22 +11502,39 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>197</v>
+        <v>421</v>
       </c>
       <c r="O65" t="n">
-        <v>197</v>
-      </c>
-      <c r="R65" t="n">
-        <v>3.504254066602351</v>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>421</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1530</t>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Lyme Disease</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -11514,6 +11542,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary Lyme disease notifications combining confirmed and probable cases under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN65" t="b">
+        <v>1</v>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -11526,12 +11612,12 @@
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1530</t>
+          <t>SER_CA_ON_PHO_IDTO_LYME_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -11539,47 +11625,47 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11692,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -11650,170 +11736,81 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>197</v>
+        <v>2143</v>
       </c>
       <c r="O66" t="n">
-        <v>197</v>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG66" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN66" t="b">
-        <v>1</v>
+        <v>2143</v>
+      </c>
+      <c r="R66" t="n">
+        <v>23.79049796631763</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -11845,12 +11842,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -11884,81 +11881,95 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>5</v>
+        <v>197</v>
       </c>
       <c r="O67" t="n">
-        <v>5</v>
+        <v>197</v>
       </c>
       <c r="R67" t="n">
-        <v>0.009689849618960231</v>
+        <v>3.504254066602351</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11985,17 +11996,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -12029,22 +12040,39 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>57</v>
+        <v>197</v>
       </c>
       <c r="O68" t="n">
-        <v>57</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1.008316220703439</v>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>197</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -12052,6 +12080,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN68" t="b">
+        <v>1</v>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -12064,12 +12150,12 @@
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
       <c r="AT68" t="n">
@@ -12077,47 +12163,47 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12144,17 +12230,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -12188,170 +12274,81 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="O69" t="n">
-        <v>57</v>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN69" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.009689849618960231</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ69" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12383,12 +12380,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -12413,7 +12410,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -12422,81 +12419,95 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.008316220703439</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12523,17 +12534,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -12558,7 +12569,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -12567,81 +12578,170 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>57</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
+        <v>1</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12703,7 +12803,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -12848,7 +12948,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -12963,12 +13063,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -12993,104 +13093,90 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>6.012374997520785</v>
+        <v>0</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13117,17 +13203,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -13152,179 +13238,90 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>338</v>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN75" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13356,12 +13353,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -13395,81 +13392,95 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>3</v>
+        <v>338</v>
       </c>
       <c r="O76" t="n">
-        <v>3</v>
+        <v>338</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005813909771376137</v>
+        <v>6.012374997520785</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13496,17 +13507,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -13540,22 +13551,39 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>101</v>
+        <v>338</v>
       </c>
       <c r="O77" t="n">
-        <v>101</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1.786665584053461</v>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>338</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -13563,6 +13591,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -13575,12 +13661,12 @@
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
       <c r="AT77" t="n">
@@ -13588,47 +13674,47 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13655,17 +13741,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -13699,170 +13785,81 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
-        <v>101</v>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG78" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN78" t="b">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.005813909771376137</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -13894,12 +13891,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -13924,7 +13921,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -13933,81 +13930,95 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.786665584053461</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14034,17 +14045,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -14069,7 +14080,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -14078,81 +14089,170 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>101</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN80" t="b">
+        <v>1</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14314,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -14359,7 +14459,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -14368,13 +14468,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -14504,7 +14604,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -14513,13 +14613,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -14619,12 +14719,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -14649,104 +14749,90 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>1.387471153274027</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14773,17 +14859,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -14808,179 +14894,90 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>78</v>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG85" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN85" t="b">
         <v>1</v>
       </c>
+      <c r="R85" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15012,12 +15009,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -15051,81 +15048,95 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="O86" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="R86" t="n">
-        <v>0.005813909771376137</v>
+        <v>1.387471153274027</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15152,17 +15163,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15196,22 +15207,39 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="O87" t="n">
-        <v>36</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0.6368312972863822</v>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>78</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -15219,6 +15247,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN87" t="b">
+        <v>1</v>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -15231,12 +15317,12 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -15244,47 +15330,47 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15311,17 +15397,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15355,170 +15441,81 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="O88" t="n">
-        <v>36</v>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD88" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG88" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN88" t="b">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.005813909771376137</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15550,118 +15547,511 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>36</v>
+      </c>
+      <c r="O89" t="n">
+        <v>36</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0.6368312972863822</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>36</v>
+      </c>
+      <c r="O90" t="n">
+        <v>36</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN90" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>D109</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Lyme disease</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
         <is>
           <t>莱姆病</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N89" t="n">
+      <c r="N91" t="n">
         <v>0</v>
       </c>
-      <c r="O89" t="n">
+      <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="R89" t="n">
+      <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO89" t="inlineStr">
+      <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP89" t="inlineStr">
+      <c r="AP91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR89" t="inlineStr">
+      <c r="AR91" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS89" t="inlineStr"/>
-      <c r="AT89" t="n">
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
         <v>0</v>
       </c>
-      <c r="AU89" t="inlineStr">
+      <c r="AU91" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV89" t="inlineStr">
+      <c r="AV91" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW89" t="inlineStr">
+      <c r="AW91" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
+      <c r="AX91" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY89" t="inlineStr">
+      <c r="AY91" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
+      <c r="AZ91" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA89" t="inlineStr">
+      <c r="BA91" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB89" t="inlineStr">
+      <c r="BB91" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC89" t="inlineStr">
+      <c r="BC91" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -15783,7 +16173,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -15793,7 +16183,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -15813,7 +16203,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -15845,7 +16235,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5770</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -12274,13 +12274,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R69" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -13785,13 +13785,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R78" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -15048,13 +15048,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="O86" t="n">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="R86" t="n">
-        <v>1.387471153274027</v>
+        <v>2.205723371871531</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -15207,10 +15207,10 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="O87" t="n">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
@@ -16052,6 +16052,151 @@
         </is>
       </c>
       <c r="BC91" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16090,7 +16235,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -16173,7 +16318,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -16183,7 +16328,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -16235,7 +16380,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6206</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O28" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="R28" t="n">
-        <v>2.908590978616528</v>
+        <v>2.897489486331732</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -7472,13 +7472,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O41" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="R41" t="n">
-        <v>4.362886467924791</v>
+        <v>4.351784975639996</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -9530,13 +9530,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="O53" t="n">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="R53" t="n">
-        <v>9.702704256911622</v>
+        <v>9.691602764626827</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -11736,13 +11736,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2143</v>
+        <v>2183</v>
       </c>
       <c r="O66" t="n">
-        <v>2143</v>
+        <v>2183</v>
       </c>
       <c r="R66" t="n">
-        <v>23.79049796631763</v>
+        <v>24.23455765770947</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -12419,13 +12419,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O70" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R70" t="n">
-        <v>1.008316220703439</v>
+        <v>0.9906264624454836</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -12578,10 +12578,10 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O71" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -13353,12 +13353,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -13392,95 +13392,81 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>338</v>
+        <v>1746</v>
       </c>
       <c r="O76" t="n">
-        <v>338</v>
+        <v>1746</v>
       </c>
       <c r="R76" t="n">
-        <v>6.012374997520785</v>
+        <v>19.38320552925365</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13493,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -13556,98 +13542,23 @@
       <c r="O77" t="n">
         <v>338</v>
       </c>
+      <c r="R77" t="n">
+        <v>6.012374997520785</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN77" t="b">
-        <v>1</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -13741,17 +13652,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -13785,81 +13696,170 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2</v>
+        <v>338</v>
       </c>
       <c r="O78" t="n">
-        <v>2</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0.003875939847584092</v>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>338</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN78" t="b">
+        <v>1</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13891,12 +13891,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -13930,95 +13930,81 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="O79" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="R79" t="n">
-        <v>1.786665584053461</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14031,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -14089,103 +14075,28 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O80" t="n">
-        <v>101</v>
+        <v>103</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1.822045100569371</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG80" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN80" t="b">
-        <v>1</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -14279,17 +14190,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -14314,7 +14225,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -14323,81 +14234,170 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>103</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -14758,13 +14758,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -15009,12 +15009,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -15039,104 +15039,90 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>2.205723371871531</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15163,7 +15149,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -15207,103 +15193,28 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="O87" t="n">
-        <v>124</v>
+        <v>138</v>
+      </c>
+      <c r="R87" t="n">
+        <v>2.45475665579251</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1530</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1530</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Lyme borreliosis</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN87" t="b">
-        <v>1</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -15397,17 +15308,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15441,81 +15352,170 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>138</v>
       </c>
       <c r="O88" t="n">
-        <v>3</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0.005813909771376137</v>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>138</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN88" t="b">
+        <v>1</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15547,12 +15547,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -15586,95 +15586,81 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="O89" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="R89" t="n">
-        <v>0.6368312972863822</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ89" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15701,7 +15687,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -15745,103 +15731,28 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="O90" t="n">
-        <v>36</v>
+        <v>58</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1.026005978961394</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_401_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Lyme borreliose</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN90" t="b">
-        <v>1</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -15935,17 +15846,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -15970,7 +15881,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -15979,81 +15890,170 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>58</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN91" t="b">
+        <v>1</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16115,7 +16115,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -16124,13 +16124,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -16197,6 +16197,151 @@
         </is>
       </c>
       <c r="BC92" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16318,7 +16463,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -16328,7 +16473,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -16380,7 +16525,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6251</v>
+        <v>8071</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -15193,13 +15193,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="O87" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="R87" t="n">
-        <v>2.45475665579251</v>
+        <v>2.632637572878924</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="O88" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8071</v>
+        <v>8081</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -15193,13 +15193,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="O87" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="R87" t="n">
-        <v>2.632637572878924</v>
+        <v>2.917247040217185</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="O88" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8081</v>
+        <v>8097</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -14075,13 +14075,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O80" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R80" t="n">
-        <v>1.822045100569371</v>
+        <v>1.839734858827326</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O81" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -15193,13 +15193,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="O87" t="n">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="R87" t="n">
-        <v>2.917247040217185</v>
+        <v>4.126837276404799</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="O88" t="n">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -15586,13 +15586,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R89" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -15731,13 +15731,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="O90" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="R90" t="n">
-        <v>1.026005978961394</v>
+        <v>1.680527034505731</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -15890,10 +15890,10 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="O91" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -16342,6 +16342,151 @@
         </is>
       </c>
       <c r="BC93" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16380,7 +16525,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16608,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -16473,7 +16618,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -16525,7 +16670,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8097</v>
+        <v>8204</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -15193,13 +15193,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="O87" t="n">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="R87" t="n">
-        <v>4.126837276404799</v>
+        <v>4.39365865203442</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="O88" t="n">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8204</v>
+        <v>8219</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1871,17 +1871,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2097,7 +2102,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2105,17 +2110,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -3921,7 +3931,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -3929,17 +3939,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4155,7 +4170,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4163,17 +4178,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -5979,7 +5999,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -5987,17 +6007,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6213,7 +6238,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
@@ -6221,17 +6246,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS33" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -8185,7 +8215,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -8193,17 +8223,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -8419,7 +8454,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -8427,17 +8462,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -10243,7 +10283,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -10251,17 +10291,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -10477,7 +10522,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -10485,17 +10530,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -12449,7 +12499,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -12457,17 +12507,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -12683,7 +12738,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -12691,17 +12746,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -14105,7 +14165,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -14113,17 +14173,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -14339,7 +14404,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -14347,17 +14412,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -15761,7 +15831,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
@@ -15769,17 +15839,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS90" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -15995,7 +16070,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
@@ -16003,17 +16078,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS91" t="inlineStr">
         <is>
           <t>SER_NO_FHI_401_MONTHLY</t>
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -13990,13 +13990,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -14135,13 +14135,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O80" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R80" t="n">
-        <v>1.839734858827326</v>
+        <v>1.857424617085282</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -14299,10 +14299,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O81" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>247</v>
+        <v>341</v>
       </c>
       <c r="O87" t="n">
-        <v>247</v>
+        <v>341</v>
       </c>
       <c r="R87" t="n">
-        <v>4.39365865203442</v>
+        <v>6.065739272646709</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15422,10 +15422,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>247</v>
+        <v>341</v>
       </c>
       <c r="O88" t="n">
-        <v>247</v>
+        <v>341</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -15656,13 +15656,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R89" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -15801,13 +15801,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="O90" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="R90" t="n">
-        <v>1.680527034505731</v>
+        <v>2.388117364823933</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -15965,10 +15965,10 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="O91" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -16569,6 +16569,1092 @@
       <c r="BC94" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Lyme borreliosis</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1530.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1530</t>
+        </is>
+      </c>
+      <c r="AT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>lyme-disease</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Lyme borreliose</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN100" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_401_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16605,7 +17691,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -16688,7 +17774,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -16698,7 +17784,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -16718,7 +17804,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -16750,7 +17836,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8219</v>
+        <v>8354</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d109/2026-2029.xlsx
+++ b/diseases/d109/2026-2029.xlsx
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="O87" t="n">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="R87" t="n">
-        <v>6.065739272646709</v>
+        <v>6.261408281441764</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15422,10 +15422,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="O88" t="n">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -15656,13 +15656,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R89" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16784,13 +16784,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -16943,10 +16943,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8354</v>
+        <v>8373</v>
       </c>
     </row>
     <row r="16">
